--- a/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/larher_chalmers_se/Documents/Documents/GitHub/oa-tskr/Bibsam_tidskriftslistor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{24ED0EC1-EDC5-4098-8724-510DC69C60FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D31DAB4-2202-4C50-9037-A5C43DCD4D82}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{24ED0EC1-EDC5-4098-8724-510DC69C60FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77CF3ADA-5629-482B-8851-15DC8C4F5C5B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="164">
   <si>
     <t>Publicera</t>
   </si>
@@ -484,6 +484,39 @@
   </si>
   <si>
     <t>https://publicera.kb.se/scis</t>
+  </si>
+  <si>
+    <t>1653-1868 </t>
+  </si>
+  <si>
+    <t>2004-5190</t>
+  </si>
+  <si>
+    <t>Educare</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/educare</t>
+  </si>
+  <si>
+    <t>1368-1613</t>
+  </si>
+  <si>
+    <t>Information Research</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/ir</t>
+  </si>
+  <si>
+    <t>2001-3345</t>
+  </si>
+  <si>
+    <t>1401-6788</t>
+  </si>
+  <si>
+    <t>Pedagogisk forskning i Sverige</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/pfs</t>
   </si>
 </sst>
 </file>
@@ -539,8 +572,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12AF23A6-2279-424C-AB87-3065524107F9}" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0">
-  <autoFilter ref="A1:G38" xr:uid="{12AF23A6-2279-424C-AB87-3065524107F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12AF23A6-2279-424C-AB87-3065524107F9}" name="Table1" displayName="Table1" ref="A1:G41" totalsRowShown="0">
+  <autoFilter ref="A1:G41" xr:uid="{12AF23A6-2279-424C-AB87-3065524107F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
+    <sortCondition ref="D1:D41"/>
+  </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{8B45EBCE-EF00-4FA6-A6ED-59A00E01B863}" name="Imprint"/>
     <tableColumn id="2" xr3:uid="{A9EB4BBA-142C-4732-A2FA-1E710C2E2A84}" name="ISSN Electronic"/>
@@ -871,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{630E83F9-1EB3-438E-B27E-DC719B2EF181}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -997,22 +1033,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="F6" t="s">
         <v>126</v>
       </c>
       <c r="G6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1020,19 +1056,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
         <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1040,19 +1079,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F8" t="s">
         <v>126</v>
       </c>
       <c r="G8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1060,22 +1099,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
         <v>126</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1083,22 +1119,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="F10" t="s">
         <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1106,22 +1142,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
         <v>126</v>
       </c>
       <c r="G11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1129,22 +1165,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F12" t="s">
         <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1152,19 +1188,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F13" t="s">
         <v>126</v>
       </c>
       <c r="G13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1172,22 +1211,19 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F14" t="s">
         <v>126</v>
       </c>
       <c r="G14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1195,22 +1231,19 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
         <v>126</v>
       </c>
       <c r="G15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1218,16 +1251,16 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
         <v>126</v>
@@ -1241,16 +1274,16 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
         <v>126</v>
@@ -1264,16 +1297,16 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F18" t="s">
         <v>126</v>
@@ -1287,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="F19" t="s">
         <v>126</v>
@@ -1310,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
         <v>126</v>
@@ -1333,16 +1366,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
         <v>126</v>
@@ -1356,16 +1389,16 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
         <v>126</v>
@@ -1379,13 +1412,16 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
         <v>126</v>
@@ -1399,16 +1435,16 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
         <v>126</v>
@@ -1422,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
         <v>126</v>
       </c>
       <c r="G25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1445,16 +1481,13 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" t="s">
-        <v>150</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
         <v>126</v>
@@ -1468,13 +1501,16 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
         <v>126</v>
@@ -1488,19 +1524,22 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
         <v>126</v>
       </c>
       <c r="G28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1508,16 +1547,16 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="F29" t="s">
         <v>126</v>
@@ -1531,16 +1570,13 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s">
         <v>126</v>
@@ -1554,16 +1590,13 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F31" t="s">
         <v>126</v>
@@ -1577,22 +1610,22 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>126</v>
       </c>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1600,16 +1633,16 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
         <v>126</v>
@@ -1623,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F34" t="s">
         <v>126</v>
@@ -1646,22 +1679,22 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E35" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
         <v>126</v>
       </c>
       <c r="G35" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1669,16 +1702,16 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F36" t="s">
         <v>126</v>
@@ -1692,16 +1725,16 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E37" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="F37" t="s">
         <v>126</v>
@@ -1715,18 +1748,87 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" t="s">
+        <v>126</v>
+      </c>
+      <c r="G38" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>89</v>
+      </c>
+      <c r="F39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G39" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" t="s">
+        <v>90</v>
+      </c>
+      <c r="F40" t="s">
+        <v>126</v>
+      </c>
+      <c r="G40" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
         <v>33</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D41" t="s">
         <v>143</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E41" t="s">
         <v>97</v>
       </c>
-      <c r="F38" t="s">
-        <v>126</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="F41" t="s">
+        <v>126</v>
+      </c>
+      <c r="G41" t="s">
         <v>127</v>
       </c>
     </row>

--- a/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/larher_chalmers_se/Documents/Documents/GitHub/oa-tskr/Bibsam_tidskriftslistor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{24ED0EC1-EDC5-4098-8724-510DC69C60FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77CF3ADA-5629-482B-8851-15DC8C4F5C5B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9463049-413A-4479-9D1E-3FC83C984BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="182">
   <si>
     <t>Publicera</t>
   </si>
@@ -517,6 +517,60 @@
   </si>
   <si>
     <t>https://publicera.kb.se/pfs</t>
+  </si>
+  <si>
+    <t>0346-7821</t>
+  </si>
+  <si>
+    <t>Arbete och Hälsa</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/aoh</t>
+  </si>
+  <si>
+    <t>2004-108X</t>
+  </si>
+  <si>
+    <t>1100-5629</t>
+  </si>
+  <si>
+    <t>ASLA:s skriftserier = ASLA Studies in Applied Linguistics</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/asla</t>
+  </si>
+  <si>
+    <t>2003-3605</t>
+  </si>
+  <si>
+    <t>Journal of Praxis in Higher Education</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/jphe</t>
+  </si>
+  <si>
+    <t>2002-3871</t>
+  </si>
+  <si>
+    <t>0348-6133</t>
+  </si>
+  <si>
+    <t>Samlaren</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/samlaren</t>
+  </si>
+  <si>
+    <t>2003-5624</t>
+  </si>
+  <si>
+    <t>1104-1420 </t>
+  </si>
+  <si>
+    <t>Socialvetenskaplig tidskrift </t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/socvet</t>
   </si>
 </sst>
 </file>
@@ -572,19 +626,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12AF23A6-2279-424C-AB87-3065524107F9}" name="Table1" displayName="Table1" ref="A1:G41" totalsRowShown="0">
-  <autoFilter ref="A1:G41" xr:uid="{12AF23A6-2279-424C-AB87-3065524107F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
-    <sortCondition ref="D1:D41"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}" name="Table2" displayName="Table2" ref="A1:G46" totalsRowShown="0">
+  <autoFilter ref="A1:G46" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8B45EBCE-EF00-4FA6-A6ED-59A00E01B863}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{A9EB4BBA-142C-4732-A2FA-1E710C2E2A84}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{BC2D1A63-1406-44B0-8054-8DC9F44098BE}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{36E67E0C-0BD5-4072-9887-F002C902EB49}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{E10FDE9C-BC07-42F8-BE24-5205C63032BC}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{306FFCAE-407B-47C3-80EB-9C4A489C7868}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{AA367428-EB06-4784-88F5-2E9714CB5458}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{55D7ADD5-2DAC-48B2-B1F8-1E6EC7E7DC60}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{7AC4022B-26A0-4825-9089-F3F28D9C4D4D}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{905E6B9D-6A3C-4A6F-B9D1-51D3B0AAE2EA}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{B36CDA97-DBAD-44E3-9FF3-9E851AB34E82}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{F0C55B3B-ED9C-4DBA-8C72-E4FE48B9CB00}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{E6108187-8193-4BCF-AD64-4FE19967AABE}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{51843F75-BE72-497E-AD92-3ED8E1EAE687}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -906,8 +957,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{630E83F9-1EB3-438E-B27E-DC719B2EF181}">
-  <dimension ref="A1:G41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68AD14AF-629B-44B1-83ED-A2A9C79A2998}">
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -986,17 +1037,14 @@
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="F4" t="s">
         <v>126</v>
@@ -1010,16 +1058,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
         <v>126</v>
@@ -1033,22 +1081,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="F6" t="s">
         <v>126</v>
       </c>
       <c r="G6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1056,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
         <v>126</v>
@@ -1079,13 +1127,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>153</v>
+      </c>
+      <c r="C8" t="s">
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="F8" t="s">
         <v>126</v>
@@ -1099,13 +1150,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
         <v>126</v>
@@ -1119,22 +1173,19 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" t="s">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="F10" t="s">
         <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1142,22 +1193,19 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
         <v>126</v>
       </c>
       <c r="G11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1165,22 +1213,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="F12" t="s">
         <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1188,22 +1236,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
         <v>126</v>
       </c>
       <c r="G13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1211,19 +1259,22 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
         <v>126</v>
       </c>
       <c r="G14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1231,19 +1282,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
         <v>126</v>
       </c>
       <c r="G15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1251,22 +1305,19 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F16" t="s">
         <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1274,22 +1325,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
         <v>126</v>
       </c>
       <c r="G17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1297,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F18" t="s">
         <v>126</v>
@@ -1320,22 +1368,19 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="F19" t="s">
         <v>126</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1343,16 +1388,16 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="F20" t="s">
         <v>126</v>
@@ -1366,16 +1411,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
         <v>126</v>
@@ -1389,16 +1434,16 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="F22" t="s">
         <v>126</v>
@@ -1412,16 +1457,16 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
         <v>126</v>
@@ -1435,16 +1480,16 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s">
         <v>126</v>
@@ -1458,16 +1503,16 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s">
         <v>126</v>
@@ -1481,13 +1526,16 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
         <v>126</v>
@@ -1501,16 +1549,16 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s">
         <v>126</v>
@@ -1524,22 +1572,22 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="F28" t="s">
         <v>126</v>
       </c>
       <c r="G28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,16 +1595,13 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>149</v>
-      </c>
-      <c r="C29" t="s">
-        <v>150</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="F29" t="s">
         <v>126</v>
@@ -1570,13 +1615,16 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s">
         <v>126</v>
@@ -1590,13 +1638,16 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>174</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="F31" t="s">
         <v>126</v>
@@ -1610,22 +1661,22 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
         <v>126</v>
       </c>
       <c r="G32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1633,16 +1684,16 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="F33" t="s">
         <v>126</v>
@@ -1656,16 +1707,13 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E34" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F34" t="s">
         <v>126</v>
@@ -1679,22 +1727,19 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F35" t="s">
         <v>126</v>
       </c>
       <c r="G35" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1702,16 +1747,16 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>126</v>
@@ -1725,16 +1770,16 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="D37" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E37" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="F37" t="s">
         <v>126</v>
@@ -1748,16 +1793,16 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
         <v>126</v>
@@ -1771,16 +1816,16 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
         <v>126</v>
@@ -1794,22 +1839,22 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F40" t="s">
         <v>126</v>
       </c>
       <c r="G40" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1817,18 +1862,133 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" t="s">
+        <v>126</v>
+      </c>
+      <c r="G41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" t="s">
+        <v>114</v>
+      </c>
+      <c r="F43" t="s">
+        <v>126</v>
+      </c>
+      <c r="G43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>89</v>
+      </c>
+      <c r="F44" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>142</v>
+      </c>
+      <c r="E45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G45" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
         <v>33</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D46" t="s">
         <v>143</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E46" t="s">
         <v>97</v>
       </c>
-      <c r="F41" t="s">
-        <v>126</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="F46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" t="s">
         <v>127</v>
       </c>
     </row>

--- a/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9463049-413A-4479-9D1E-3FC83C984BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED29E3A-9140-47B3-A707-F1BDA6A3CF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="186">
   <si>
     <t>Publicera</t>
   </si>
@@ -534,9 +534,6 @@
     <t>1100-5629</t>
   </si>
   <si>
-    <t>ASLA:s skriftserier = ASLA Studies in Applied Linguistics</t>
-  </si>
-  <si>
     <t>https://publicera.kb.se/asla</t>
   </si>
   <si>
@@ -571,6 +568,21 @@
   </si>
   <si>
     <t>https://publicera.kb.se/socvet</t>
+  </si>
+  <si>
+    <t>ASLA:s skriftserie = ASLA Studies in Applied Linguistics</t>
+  </si>
+  <si>
+    <t>3035-6903</t>
+  </si>
+  <si>
+    <t>Current Issues in Work-Integrated Learning</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/ciwil</t>
+  </si>
+  <si>
+    <t>CC BY</t>
   </si>
 </sst>
 </file>
@@ -626,8 +638,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}" name="Table2" displayName="Table2" ref="A1:G46" totalsRowShown="0">
-  <autoFilter ref="A1:G46" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}" name="Table2" displayName="Table2" ref="A1:G47" totalsRowShown="0">
+  <autoFilter ref="A1:G47" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G47">
+    <sortCondition ref="D1:D47"/>
+  </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{55D7ADD5-2DAC-48B2-B1F8-1E6EC7E7DC60}" name="Imprint"/>
     <tableColumn id="2" xr3:uid="{7AC4022B-26A0-4825-9089-F3F28D9C4D4D}" name="ISSN Electronic"/>
@@ -958,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68AD14AF-629B-44B1-83ED-A2A9C79A2998}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -1087,10 +1102,10 @@
         <v>168</v>
       </c>
       <c r="D6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" t="s">
         <v>169</v>
-      </c>
-      <c r="E6" t="s">
-        <v>170</v>
       </c>
       <c r="F6" t="s">
         <v>126</v>
@@ -1104,22 +1119,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="F7" t="s">
         <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1127,22 +1139,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="F8" t="s">
         <v>126</v>
       </c>
       <c r="G8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1150,22 +1162,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
         <v>126</v>
       </c>
       <c r="G9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1173,19 +1185,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
         <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1193,19 +1208,19 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
         <v>126</v>
       </c>
       <c r="G11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1213,22 +1228,19 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
         <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1236,22 +1248,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="F13" t="s">
         <v>126</v>
       </c>
       <c r="G13" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1259,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
         <v>126</v>
       </c>
       <c r="G14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,22 +1294,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s">
         <v>126</v>
       </c>
       <c r="G15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1305,13 +1317,16 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>157</v>
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
         <v>126</v>
@@ -1325,19 +1340,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="F17" t="s">
         <v>126</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1345,22 +1360,19 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
         <v>126</v>
       </c>
       <c r="G18" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1368,19 +1380,22 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>173</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
         <v>126</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1388,22 +1403,19 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="F20" t="s">
         <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1411,16 +1423,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
         <v>126</v>
@@ -1434,16 +1446,16 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s">
         <v>126</v>
@@ -1457,16 +1469,16 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F23" t="s">
         <v>126</v>
@@ -1480,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
         <v>126</v>
@@ -1503,16 +1515,16 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
         <v>126</v>
@@ -1526,16 +1538,16 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
         <v>126</v>
@@ -1549,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s">
         <v>126</v>
@@ -1572,16 +1584,16 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="E28" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
         <v>126</v>
@@ -1595,13 +1607,16 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>160</v>
+      </c>
+      <c r="C29" t="s">
+        <v>161</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
         <v>126</v>
@@ -1615,16 +1630,13 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
         <v>126</v>
@@ -1638,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s">
-        <v>177</v>
+        <v>93</v>
       </c>
       <c r="F31" t="s">
         <v>126</v>
@@ -1661,22 +1673,22 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s">
         <v>126</v>
       </c>
       <c r="G32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1684,22 +1696,22 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s">
         <v>126</v>
       </c>
       <c r="G33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1707,13 +1719,16 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>149</v>
+      </c>
+      <c r="C34" t="s">
+        <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="F34" t="s">
         <v>126</v>
@@ -1727,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
         <v>126</v>
@@ -1747,16 +1762,13 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s">
         <v>126</v>
@@ -1770,16 +1782,16 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>178</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>179</v>
+        <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
         <v>126</v>
@@ -1793,16 +1805,16 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="E38" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="F38" t="s">
         <v>126</v>
@@ -1816,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
         <v>126</v>
@@ -1839,22 +1851,22 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="F40" t="s">
         <v>126</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1862,22 +1874,22 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
         <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1885,16 +1897,16 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="F42" t="s">
         <v>126</v>
@@ -1908,16 +1920,16 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E43" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F43" t="s">
         <v>126</v>
@@ -1931,16 +1943,16 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F44" t="s">
         <v>126</v>
@@ -1954,16 +1966,16 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F45" t="s">
         <v>126</v>
@@ -1977,18 +1989,41 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" t="s">
+        <v>142</v>
+      </c>
+      <c r="E46" t="s">
+        <v>90</v>
+      </c>
+      <c r="F46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
         <v>33</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>143</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E47" t="s">
         <v>97</v>
       </c>
-      <c r="F46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="F47" t="s">
+        <v>126</v>
+      </c>
+      <c r="G47" t="s">
         <v>127</v>
       </c>
     </row>

--- a/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED29E3A-9140-47B3-A707-F1BDA6A3CF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE1F3DC-1C63-479C-B1E6-A7B48062720C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="198">
   <si>
     <t>Publicera</t>
   </si>
@@ -583,6 +583,42 @@
   </si>
   <si>
     <t>CC BY</t>
+  </si>
+  <si>
+    <t>3035-9821</t>
+  </si>
+  <si>
+    <t>2004–9811</t>
+  </si>
+  <si>
+    <t>Childhood in the Anthropocene </t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/cia</t>
+  </si>
+  <si>
+    <t>2002-4223</t>
+  </si>
+  <si>
+    <t>1650-1519</t>
+  </si>
+  <si>
+    <t>Journal of Nordic Archaeological Science </t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/jonas</t>
+  </si>
+  <si>
+    <t>2004-7142</t>
+  </si>
+  <si>
+    <t>2000-0898</t>
+  </si>
+  <si>
+    <t>Opuscula. Annual of the Swedish Institutes at Athens and Rome</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/opuscula</t>
   </si>
 </sst>
 </file>
@@ -638,19 +674,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}" name="Table2" displayName="Table2" ref="A1:G47" totalsRowShown="0">
-  <autoFilter ref="A1:G47" xr:uid="{D65EF0CE-8F76-4F72-8231-DB685390B91D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G47">
-    <sortCondition ref="D1:D47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{649C6ACC-3253-4711-80EB-F68837A7873B}" name="Table1" displayName="Table1" ref="A1:G50" totalsRowShown="0">
+  <autoFilter ref="A1:G50" xr:uid="{649C6ACC-3253-4711-80EB-F68837A7873B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G50">
+    <sortCondition ref="D1:D50"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{55D7ADD5-2DAC-48B2-B1F8-1E6EC7E7DC60}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{7AC4022B-26A0-4825-9089-F3F28D9C4D4D}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{905E6B9D-6A3C-4A6F-B9D1-51D3B0AAE2EA}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{B36CDA97-DBAD-44E3-9FF3-9E851AB34E82}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{F0C55B3B-ED9C-4DBA-8C72-E4FE48B9CB00}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{E6108187-8193-4BCF-AD64-4FE19967AABE}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{51843F75-BE72-497E-AD92-3ED8E1EAE687}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{3DD7F4A1-8BB9-4F47-A388-59EE629677FD}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{F0B9E6CD-47AD-41A0-8F05-C042FFBF1BC2}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{0C1F77FE-F2B9-47E3-B6BB-5A3D5FB3CAE4}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{B43D4A97-8118-4787-9793-BFFE455580D9}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{2C6FD05A-BE8F-43D9-A0A2-A00591B53601}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{8F79A6DD-4F18-4D96-B71F-F88BD4F09A98}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{A8DE93DC-A860-4925-B2F1-486E668E3A2E}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -972,8 +1008,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68AD14AF-629B-44B1-83ED-A2A9C79A2998}">
-  <dimension ref="A1:G47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476B91EB-9788-4BC2-AC83-38639335D593}">
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -1052,6 +1088,9 @@
       <c r="A4" t="s">
         <v>0</v>
       </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
@@ -1119,13 +1158,13 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F7" t="s">
         <v>126</v>
@@ -1139,22 +1178,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="F8" t="s">
         <v>126</v>
       </c>
       <c r="G8" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1162,22 +1198,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
         <v>126</v>
       </c>
       <c r="G9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1185,22 +1221,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="F10" t="s">
         <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1208,19 +1244,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
         <v>126</v>
       </c>
       <c r="G11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1228,19 +1267,19 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F12" t="s">
         <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1248,22 +1287,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
         <v>126</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1271,22 +1307,22 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="F14" t="s">
         <v>126</v>
       </c>
       <c r="G14" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1294,22 +1330,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F15" t="s">
         <v>126</v>
       </c>
       <c r="G15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1317,22 +1353,22 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s">
         <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1340,13 +1376,16 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
         <v>126</v>
@@ -1360,19 +1399,19 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="F18" t="s">
         <v>126</v>
       </c>
       <c r="G18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1380,22 +1419,19 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" t="s">
         <v>126</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1403,19 +1439,22 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
         <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1423,22 +1462,22 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="E21" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="F21" t="s">
         <v>126</v>
       </c>
       <c r="G21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1446,22 +1485,19 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="F22" t="s">
         <v>126</v>
       </c>
       <c r="G22" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1469,16 +1505,16 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
         <v>126</v>
@@ -1492,16 +1528,16 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s">
         <v>126</v>
@@ -1515,16 +1551,16 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s">
         <v>126</v>
@@ -1538,16 +1574,16 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
         <v>126</v>
@@ -1561,16 +1597,16 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
         <v>126</v>
@@ -1584,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
         <v>126</v>
@@ -1607,16 +1643,16 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s">
         <v>126</v>
@@ -1630,13 +1666,16 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E30" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F30" t="s">
         <v>126</v>
@@ -1650,16 +1689,16 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="F31" t="s">
         <v>126</v>
@@ -1673,16 +1712,16 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="F32" t="s">
         <v>126</v>
@@ -1696,22 +1735,19 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F33" t="s">
         <v>126</v>
       </c>
       <c r="G33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1719,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
-        <v>152</v>
+        <v>93</v>
       </c>
       <c r="F34" t="s">
         <v>126</v>
@@ -1742,13 +1778,16 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>173</v>
+      </c>
+      <c r="C35" t="s">
+        <v>174</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="E35" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="F35" t="s">
         <v>126</v>
@@ -1762,19 +1801,22 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F36" t="s">
         <v>126</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1782,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="F37" t="s">
         <v>126</v>
@@ -1805,16 +1847,13 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
-      </c>
-      <c r="C38" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="E38" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="F38" t="s">
         <v>126</v>
@@ -1828,16 +1867,13 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F39" t="s">
         <v>126</v>
@@ -1851,16 +1887,16 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F40" t="s">
         <v>126</v>
@@ -1874,22 +1910,22 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="C41" t="s">
-        <v>1</v>
+        <v>178</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="E41" t="s">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="F41" t="s">
         <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1897,16 +1933,16 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D42" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E42" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="F42" t="s">
         <v>126</v>
@@ -1920,16 +1956,16 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F43" t="s">
         <v>126</v>
@@ -1943,22 +1979,22 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E44" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="F44" t="s">
         <v>126</v>
       </c>
       <c r="G44" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1966,16 +2002,16 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="E45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F45" t="s">
         <v>126</v>
@@ -1989,16 +2025,16 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="F46" t="s">
         <v>126</v>
@@ -2012,18 +2048,87 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" t="s">
+        <v>126</v>
+      </c>
+      <c r="G47" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G48" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" t="s">
+        <v>142</v>
+      </c>
+      <c r="E49" t="s">
+        <v>90</v>
+      </c>
+      <c r="F49" t="s">
+        <v>126</v>
+      </c>
+      <c r="G49" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
         <v>33</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D50" t="s">
         <v>143</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E50" t="s">
         <v>97</v>
       </c>
-      <c r="F47" t="s">
-        <v>126</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="F50" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" t="s">
         <v>127</v>
       </c>
     </row>

--- a/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_publicera.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE1F3DC-1C63-479C-B1E6-A7B48062720C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FA9AC5-9B0D-44AC-9273-559BE6000850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="217">
   <si>
     <t>Publicera</t>
   </si>
@@ -619,6 +619,63 @@
   </si>
   <si>
     <t>https://publicera.kb.se/opuscula</t>
+  </si>
+  <si>
+    <t>3035-9880</t>
+  </si>
+  <si>
+    <t> 0349-8808</t>
+  </si>
+  <si>
+    <t>Adoranten</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/adoranten</t>
+  </si>
+  <si>
+    <t>2002-4665</t>
+  </si>
+  <si>
+    <t>European Journal of Philosophy in Arts Education</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/ejpae</t>
+  </si>
+  <si>
+    <t>1404-9430</t>
+  </si>
+  <si>
+    <t>0015-7813</t>
+  </si>
+  <si>
+    <t>Fornvännen: Journal of Swedish Antiquarian Research</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/fornvannen</t>
+  </si>
+  <si>
+    <t>2004-3929</t>
+  </si>
+  <si>
+    <t>2000-9216</t>
+  </si>
+  <si>
+    <t>Högskolepedagogisk debatt</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/hpdebatt</t>
+  </si>
+  <si>
+    <t>2001-7286</t>
+  </si>
+  <si>
+    <t>1100-2573</t>
+  </si>
+  <si>
+    <t>lambda nordica</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/lambdanordica</t>
   </si>
 </sst>
 </file>
@@ -674,19 +731,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{649C6ACC-3253-4711-80EB-F68837A7873B}" name="Table1" displayName="Table1" ref="A1:G50" totalsRowShown="0">
-  <autoFilter ref="A1:G50" xr:uid="{649C6ACC-3253-4711-80EB-F68837A7873B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G50">
-    <sortCondition ref="D1:D50"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{932C8EC6-1716-4305-8EFE-F62E4A55370B}" name="Table1" displayName="Table1" ref="A1:G55" totalsRowShown="0">
+  <autoFilter ref="A1:G55" xr:uid="{932C8EC6-1716-4305-8EFE-F62E4A55370B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{3DD7F4A1-8BB9-4F47-A388-59EE629677FD}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{F0B9E6CD-47AD-41A0-8F05-C042FFBF1BC2}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{0C1F77FE-F2B9-47E3-B6BB-5A3D5FB3CAE4}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{B43D4A97-8118-4787-9793-BFFE455580D9}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{2C6FD05A-BE8F-43D9-A0A2-A00591B53601}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{8F79A6DD-4F18-4D96-B71F-F88BD4F09A98}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{A8DE93DC-A860-4925-B2F1-486E668E3A2E}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{4839C21D-7E45-4402-B3FE-1621BA5807B5}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{7FFC0D28-96C4-4F5A-9100-50F8E3F1F610}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{0282195A-63EE-4ED2-B5F4-E65FCB121D6A}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{F83AD47D-251B-43C8-9969-0CB38B8224DB}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{C1FBC942-1E33-472E-94F2-D3FCB6416DB6}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{FDCFD5EB-804D-4BA9-8834-B7C4D401B750}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{7AA85751-A13C-47EC-8279-8E12AC69A7A6}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1008,14 +1062,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476B91EB-9788-4BC2-AC83-38639335D593}">
-  <dimension ref="A1:G50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D4ADF7-EE5A-415C-BA1B-2BE0CE283F91}">
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -1069,13 +1123,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>198</v>
+      </c>
+      <c r="C3" t="s">
+        <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
       <c r="F3" t="s">
         <v>126</v>
@@ -1089,16 +1146,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
         <v>126</v>
@@ -1112,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="F5" t="s">
         <v>126</v>
@@ -1135,16 +1189,16 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
         <v>126</v>
@@ -1158,19 +1212,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>167</v>
+      </c>
+      <c r="C7" t="s">
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="F7" t="s">
         <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1178,13 +1235,13 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F8" t="s">
         <v>126</v>
@@ -1198,22 +1255,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="F9" t="s">
         <v>126</v>
       </c>
       <c r="G9" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1221,22 +1275,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
         <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="F11" t="s">
         <v>126</v>
       </c>
       <c r="G11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1267,19 +1321,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
         <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1287,19 +1344,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
         <v>126</v>
       </c>
       <c r="G13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1307,22 +1364,19 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="F14" t="s">
         <v>126</v>
       </c>
       <c r="G14" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1330,22 +1384,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="F15" t="s">
         <v>126</v>
       </c>
       <c r="G15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1353,16 +1407,13 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="F16" t="s">
         <v>126</v>
@@ -1376,22 +1427,22 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="F17" t="s">
         <v>126</v>
       </c>
       <c r="G17" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1399,19 +1450,22 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
         <v>126</v>
       </c>
       <c r="G18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1419,19 +1473,22 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>209</v>
+      </c>
+      <c r="C19" t="s">
+        <v>210</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="F19" t="s">
         <v>126</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1439,16 +1496,16 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
         <v>126</v>
@@ -1462,16 +1519,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
         <v>126</v>
@@ -1485,19 +1542,19 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F22" t="s">
         <v>126</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1505,22 +1562,19 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s">
         <v>126</v>
       </c>
       <c r="G23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1528,16 +1582,16 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s">
         <v>126</v>
@@ -1551,22 +1605,22 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="F25" t="s">
         <v>126</v>
       </c>
       <c r="G25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1574,22 +1628,19 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="F26" t="s">
         <v>126</v>
       </c>
       <c r="G26" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1597,16 +1648,16 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="F27" t="s">
         <v>126</v>
@@ -1620,16 +1671,16 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
         <v>126</v>
@@ -1643,16 +1694,16 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>214</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>215</v>
       </c>
       <c r="E29" t="s">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="F29" t="s">
         <v>126</v>
@@ -1666,16 +1717,16 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
         <v>126</v>
@@ -1689,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>196</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>197</v>
+        <v>85</v>
       </c>
       <c r="F31" t="s">
         <v>126</v>
@@ -1712,16 +1763,16 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>163</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s">
         <v>126</v>
@@ -1735,13 +1786,16 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F33" t="s">
         <v>126</v>
@@ -1755,16 +1809,16 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
         <v>126</v>
@@ -1778,16 +1832,16 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="F35" t="s">
         <v>126</v>
@@ -1801,22 +1855,22 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>194</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>196</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="F36" t="s">
         <v>126</v>
       </c>
       <c r="G36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1824,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
         <v>126</v>
@@ -1847,13 +1901,13 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F38" t="s">
         <v>126</v>
@@ -1867,13 +1921,16 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
         <v>126</v>
@@ -1887,16 +1944,16 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>174</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="F40" t="s">
         <v>126</v>
@@ -1910,22 +1967,22 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="F41" t="s">
         <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1933,16 +1990,16 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="F42" t="s">
         <v>126</v>
@@ -1956,16 +2013,13 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F43" t="s">
         <v>126</v>
@@ -1979,22 +2033,19 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F44" t="s">
         <v>126</v>
       </c>
       <c r="G44" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2002,16 +2053,16 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F45" t="s">
         <v>126</v>
@@ -2025,16 +2076,16 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="E46" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="F46" t="s">
         <v>126</v>
@@ -2048,16 +2099,16 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F47" t="s">
         <v>126</v>
@@ -2071,16 +2122,16 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E48" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F48" t="s">
         <v>126</v>
@@ -2094,22 +2145,22 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E49" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s">
         <v>126</v>
       </c>
       <c r="G49" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2117,18 +2168,133 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>83</v>
+      </c>
+      <c r="C51" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" t="s">
+        <v>118</v>
+      </c>
+      <c r="F51" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" t="s">
+        <v>135</v>
+      </c>
+      <c r="E52" t="s">
+        <v>114</v>
+      </c>
+      <c r="F52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>89</v>
+      </c>
+      <c r="F53" t="s">
+        <v>126</v>
+      </c>
+      <c r="G53" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s">
+        <v>90</v>
+      </c>
+      <c r="F54" t="s">
+        <v>126</v>
+      </c>
+      <c r="G54" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
         <v>33</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D55" t="s">
         <v>143</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E55" t="s">
         <v>97</v>
       </c>
-      <c r="F50" t="s">
-        <v>126</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="F55" t="s">
+        <v>126</v>
+      </c>
+      <c r="G55" t="s">
         <v>127</v>
       </c>
     </row>
